--- a/funnel/internal/downloads/ph-solar-competitive-landscape.xlsx
+++ b/funnel/internal/downloads/ph-solar-competitive-landscape.xlsx
@@ -601,6 +601,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
@@ -611,7 +612,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Competitive research for Solar City / BADJJ Model B (source &amp; install) positioning.</t>
+          <t>Competitive research for MACC Model B (source &amp; install) positioning.</t>
         </is>
       </c>
     </row>
@@ -622,6 +623,7 @@
         </is>
       </c>
     </row>
+    <row r="7"/>
     <row r="8">
       <c r="A8" s="3" t="inlineStr">
         <is>
@@ -678,6 +680,7 @@
         </is>
       </c>
     </row>
+    <row r="16"/>
     <row r="17">
       <c r="A17" s="3" t="inlineStr">
         <is>
@@ -727,6 +730,7 @@
         </is>
       </c>
     </row>
+    <row r="24"/>
     <row r="25">
       <c r="A25" s="3" t="inlineStr">
         <is>
@@ -737,7 +741,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Brand: Solar City (public) / BADJJ Energy Systems (internal Command Center)</t>
+          <t>Brand: MACC Systems &amp; Engineering Inc. (one name, public and internal)</t>
         </is>
       </c>
     </row>
@@ -762,6 +766,7 @@
         </is>
       </c>
     </row>
+    <row r="30"/>
     <row r="31">
       <c r="A31" s="7" t="inlineStr">
         <is>
@@ -804,6 +809,7 @@
         </is>
       </c>
     </row>
+    <row r="37"/>
     <row r="38">
       <c r="A38" s="8" t="inlineStr">
         <is>
@@ -818,6 +824,7 @@
         </is>
       </c>
     </row>
+    <row r="40"/>
     <row r="41">
       <c r="A41" s="8" t="inlineStr">
         <is>
@@ -3608,6 +3615,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="13" t="inlineStr">
         <is>
@@ -4020,6 +4028,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="13" t="inlineStr">
         <is>
@@ -4399,6 +4408,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="13" t="inlineStr">
         <is>
@@ -6093,6 +6103,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="13" t="inlineStr">
         <is>
@@ -6848,6 +6859,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="13" t="inlineStr">
         <is>
@@ -7794,6 +7806,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="13" t="inlineStr">
         <is>
@@ -8650,6 +8663,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="8" t="inlineStr">
         <is>
@@ -8776,6 +8790,7 @@
         </is>
       </c>
     </row>
+    <row r="12"/>
     <row r="13">
       <c r="A13" s="8" t="inlineStr">
         <is>
@@ -14663,7 +14678,7 @@
     <row r="46">
       <c r="A46" s="5" t="inlineStr">
         <is>
-          <t>SOLAR CITY / BADJJ</t>
+          <t>MACC</t>
         </is>
       </c>
       <c r="B46" s="5" t="inlineStr">
@@ -14722,7 +14737,7 @@
     <row r="47">
       <c r="A47" s="5" t="inlineStr">
         <is>
-          <t>SOLAR CITY / BADJJ</t>
+          <t>MACC</t>
         </is>
       </c>
       <c r="B47" s="5" t="inlineStr">
@@ -14781,7 +14796,7 @@
     <row r="48">
       <c r="A48" s="5" t="inlineStr">
         <is>
-          <t>SOLAR CITY / BADJJ</t>
+          <t>MACC</t>
         </is>
       </c>
       <c r="B48" s="5" t="inlineStr">
@@ -15340,6 +15355,7 @@
         </is>
       </c>
     </row>
+    <row r="16"/>
     <row r="17">
       <c r="A17" s="6" t="inlineStr">
         <is>
